--- a/dados/perfis/00Old/engenharia_computacao_2026_1/matriz_curricular.xlsx
+++ b/dados/perfis/00Old/engenharia_computacao_2026_1/matriz_curricular.xlsx
@@ -1,10 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+  <workbookPr codeName="EstaPastaDeTrabalho"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="288" windowWidth="23232" windowHeight="12576" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curso" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equivalencias" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -57,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -416,12 +415,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Planilha1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -466,12 +465,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Planilha2">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P160"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N160"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="13.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="36.88671875" customWidth="1" min="2" max="2"/>
+    <col width="23" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="7.77734375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="12.109375" bestFit="1" customWidth="1" min="5" max="6"/>
+    <col width="16.5546875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="15.5546875" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="44.5546875" bestFit="1" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -506,50 +516,40 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>codigo_provisorio</t>
+          <t>cht</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>cht</t>
+          <t>chp</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>chp</t>
+          <t>chd</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>chd</t>
+          <t>che</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>che</t>
+          <t>tot</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>tot</t>
+          <t>nucleo_id</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>nucleo_id</t>
+          <t>ementa</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>unidade_oferta</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ementa</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>observacoes</t>
         </is>
@@ -577,11 +577,11 @@
       <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
-        <v>0</v>
+      <c r="G2" t="n">
+        <v>60</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -590,12 +590,9 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>60</v>
-      </c>
-      <c r="O2" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>FAGEN39401 Empreendorismo e Inovação</t>
         </is>
@@ -626,25 +623,22 @@
       <c r="F3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
+      <c r="G3" t="n">
+        <v>45</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>45</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>45</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -672,25 +666,22 @@
       <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
+      <c r="G4" t="n">
+        <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>60</v>
-      </c>
-      <c r="O4" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>FEELT!ED Estrutura de Dados</t>
         </is>
@@ -718,11 +709,11 @@
       <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
+      <c r="G5" t="n">
+        <v>60</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -731,12 +722,9 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>60</v>
-      </c>
-      <c r="O5" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>FEELT!AA Análise de Algoritmos</t>
         </is>
@@ -767,11 +755,11 @@
       <c r="F6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="b">
-        <v>1</v>
+      <c r="G6" t="n">
+        <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -780,17 +768,14 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>60</v>
+        <v>60</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
         <is>
           <t>Inventivo|Meticuloso|Orientado por Propósito</t>
         </is>
@@ -821,25 +806,22 @@
       <c r="F7" t="b">
         <v>1</v>
       </c>
-      <c r="G7" t="b">
-        <v>1</v>
+      <c r="G7" t="n">
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
         <v>45</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -870,25 +852,22 @@
       <c r="F8" t="b">
         <v>1</v>
       </c>
-      <c r="G8" t="b">
-        <v>1</v>
+      <c r="G8" t="n">
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
         <v>45</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -916,11 +895,11 @@
       <c r="F9" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
+      <c r="G9" t="n">
+        <v>60</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -929,12 +908,9 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-      <c r="O9" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>FEELT31724 Redes de Comunicações I</t>
         </is>
@@ -962,25 +938,22 @@
       <c r="F10" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
+      <c r="G10" t="n">
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>30</v>
       </c>
       <c r="I10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>60</v>
-      </c>
-      <c r="O10" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>FEELT31831 Redes de Comunicações II</t>
         </is>
@@ -1011,30 +984,27 @@
       <c r="F11" t="b">
         <v>1</v>
       </c>
-      <c r="G11" t="b">
-        <v>1</v>
+      <c r="G11" t="n">
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I11" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>60</v>
+        <v>60</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
         <is>
           <t>Meticuloso|Adaptável|Inventivo</t>
         </is>
@@ -1065,11 +1035,11 @@
       <c r="F12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" t="b">
-        <v>1</v>
+      <c r="G12" t="n">
+        <v>60</v>
       </c>
       <c r="H12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1078,12 +1048,9 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>60</v>
-      </c>
-      <c r="M12" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -1114,25 +1081,22 @@
       <c r="F13" t="b">
         <v>0</v>
       </c>
-      <c r="G13" t="b">
-        <v>1</v>
+      <c r="G13" t="n">
+        <v>45</v>
       </c>
       <c r="H13" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>60</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -1160,13 +1124,10 @@
       <c r="F14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K14" t="n">
         <v>90</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>COMPLEMENTAR</t>
         </is>
@@ -1194,13 +1155,10 @@
       <c r="F15" t="b">
         <v>1</v>
       </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K15" t="n">
         <v>300</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -1231,7 +1189,7 @@
       <c r="F16" t="b">
         <v>0</v>
       </c>
-      <c r="G16" t="b">
+      <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
@@ -1241,15 +1199,12 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K16" t="n">
         <v>90</v>
       </c>
-      <c r="L16" t="n">
-        <v>90</v>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
@@ -1280,7 +1235,7 @@
       <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="G17" t="b">
+      <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
@@ -1290,15 +1245,12 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K17" t="n">
         <v>90</v>
       </c>
-      <c r="L17" t="n">
-        <v>90</v>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
@@ -1329,7 +1281,7 @@
       <c r="F18" t="b">
         <v>0</v>
       </c>
-      <c r="G18" t="b">
+      <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
@@ -1339,15 +1291,12 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K18" t="n">
         <v>75</v>
       </c>
-      <c r="L18" t="n">
-        <v>75</v>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
@@ -1378,7 +1327,7 @@
       <c r="F19" t="b">
         <v>0</v>
       </c>
-      <c r="G19" t="b">
+      <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
@@ -1388,15 +1337,12 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K19" t="n">
         <v>60</v>
       </c>
-      <c r="L19" t="n">
-        <v>60</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
@@ -1427,25 +1373,22 @@
       <c r="F20" t="b">
         <v>1</v>
       </c>
-      <c r="G20" t="b">
-        <v>1</v>
+      <c r="G20" t="n">
+        <v>15</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I20" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>60</v>
-      </c>
-      <c r="M20" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -1473,11 +1416,11 @@
       <c r="F21" t="b">
         <v>0</v>
       </c>
-      <c r="G21" t="b">
-        <v>0</v>
+      <c r="G21" t="n">
+        <v>60</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1486,9 +1429,6 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1517,25 +1457,22 @@
       <c r="F22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="b">
-        <v>0</v>
+      <c r="G22" t="n">
+        <v>90</v>
       </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>90</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>90</v>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -1566,25 +1503,22 @@
       <c r="F23" t="b">
         <v>1</v>
       </c>
-      <c r="G23" t="b">
-        <v>0</v>
+      <c r="G23" t="n">
+        <v>90</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>90</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>90</v>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -1615,25 +1549,22 @@
       <c r="F24" t="b">
         <v>1</v>
       </c>
-      <c r="G24" t="b">
-        <v>0</v>
+      <c r="G24" t="n">
+        <v>90</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>90</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>90</v>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -1664,11 +1595,11 @@
       <c r="F25" t="b">
         <v>1</v>
       </c>
-      <c r="G25" t="b">
-        <v>0</v>
+      <c r="G25" t="n">
+        <v>60</v>
       </c>
       <c r="H25" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1677,12 +1608,9 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>60</v>
-      </c>
-      <c r="M25" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -1710,22 +1638,19 @@
       <c r="F26" t="b">
         <v>0</v>
       </c>
-      <c r="G26" t="b">
-        <v>0</v>
+      <c r="G26" t="n">
+        <v>30</v>
       </c>
       <c r="H26" t="n">
         <v>30</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1751,22 +1676,19 @@
       <c r="F27" t="b">
         <v>0</v>
       </c>
-      <c r="G27" t="b">
-        <v>0</v>
+      <c r="G27" t="n">
+        <v>30</v>
       </c>
       <c r="H27" t="n">
         <v>30</v>
       </c>
       <c r="I27" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1792,11 +1714,11 @@
       <c r="F28" t="b">
         <v>1</v>
       </c>
-      <c r="G28" t="b">
-        <v>0</v>
+      <c r="G28" t="n">
+        <v>60</v>
       </c>
       <c r="H28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1805,12 +1727,9 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>60</v>
-      </c>
-      <c r="O28" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>IERI39601 Engenharia Econômica</t>
         </is>
@@ -1838,11 +1757,11 @@
       <c r="F29" t="b">
         <v>1</v>
       </c>
-      <c r="G29" t="b">
-        <v>0</v>
+      <c r="G29" t="n">
+        <v>60</v>
       </c>
       <c r="H29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1851,12 +1770,9 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>60</v>
-      </c>
-      <c r="O29" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>IERI39601 Engenharia Econômica</t>
         </is>
@@ -1884,11 +1800,11 @@
       <c r="F30" t="b">
         <v>0</v>
       </c>
-      <c r="G30" t="b">
-        <v>0</v>
+      <c r="G30" t="n">
+        <v>60</v>
       </c>
       <c r="H30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1897,9 +1813,6 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1925,11 +1838,11 @@
       <c r="F31" t="b">
         <v>0</v>
       </c>
-      <c r="G31" t="b">
-        <v>0</v>
+      <c r="G31" t="n">
+        <v>60</v>
       </c>
       <c r="H31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1938,9 +1851,6 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1966,22 +1876,19 @@
       <c r="F32" t="b">
         <v>0</v>
       </c>
-      <c r="G32" t="b">
+      <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I32" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2010,25 +1917,22 @@
       <c r="F33" t="b">
         <v>1</v>
       </c>
-      <c r="G33" t="b">
-        <v>0</v>
+      <c r="G33" t="n">
+        <v>75</v>
       </c>
       <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>75</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>75</v>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -2059,25 +1963,22 @@
       <c r="F34" t="b">
         <v>1</v>
       </c>
-      <c r="G34" t="b">
+      <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>15</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>15</v>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -2105,22 +2006,19 @@
       <c r="F35" t="b">
         <v>0</v>
       </c>
-      <c r="G35" t="b">
-        <v>1</v>
+      <c r="G35" t="n">
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J35" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
         <v>45</v>
       </c>
     </row>
@@ -2146,11 +2044,11 @@
       <c r="F36" t="b">
         <v>0</v>
       </c>
-      <c r="G36" t="b">
-        <v>0</v>
+      <c r="G36" t="n">
+        <v>60</v>
       </c>
       <c r="H36" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2159,9 +2057,6 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2190,25 +2085,22 @@
       <c r="F37" t="b">
         <v>0</v>
       </c>
-      <c r="G37" t="b">
-        <v>1</v>
+      <c r="G37" t="n">
+        <v>30</v>
       </c>
       <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>30</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>30</v>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
@@ -2236,22 +2128,19 @@
       <c r="F38" t="b">
         <v>0</v>
       </c>
-      <c r="G38" t="b">
-        <v>1</v>
+      <c r="G38" t="n">
+        <v>30</v>
       </c>
       <c r="H38" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
         <v>45</v>
       </c>
     </row>
@@ -2277,11 +2166,11 @@
       <c r="F39" t="b">
         <v>0</v>
       </c>
-      <c r="G39" t="b">
-        <v>0</v>
+      <c r="G39" t="n">
+        <v>60</v>
       </c>
       <c r="H39" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2290,9 +2179,6 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2318,11 +2204,11 @@
       <c r="F40" t="b">
         <v>0</v>
       </c>
-      <c r="G40" t="b">
-        <v>0</v>
+      <c r="G40" t="n">
+        <v>60</v>
       </c>
       <c r="H40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2331,9 +2217,6 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2359,22 +2242,19 @@
       <c r="F41" t="b">
         <v>0</v>
       </c>
-      <c r="G41" t="b">
-        <v>0</v>
+      <c r="G41" t="n">
+        <v>30</v>
       </c>
       <c r="H41" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
         <v>45</v>
       </c>
     </row>
@@ -2400,22 +2280,19 @@
       <c r="F42" t="b">
         <v>0</v>
       </c>
-      <c r="G42" t="b">
-        <v>1</v>
+      <c r="G42" t="n">
+        <v>30</v>
       </c>
       <c r="H42" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
         <v>45</v>
       </c>
     </row>
@@ -2441,11 +2318,11 @@
       <c r="F43" t="b">
         <v>0</v>
       </c>
-      <c r="G43" t="b">
-        <v>0</v>
+      <c r="G43" t="n">
+        <v>60</v>
       </c>
       <c r="H43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2454,9 +2331,6 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2482,22 +2356,19 @@
       <c r="F44" t="b">
         <v>0</v>
       </c>
-      <c r="G44" t="b">
-        <v>0</v>
+      <c r="G44" t="n">
+        <v>30</v>
       </c>
       <c r="H44" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I44" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
         <v>45</v>
       </c>
     </row>
@@ -2523,11 +2394,11 @@
       <c r="F45" t="b">
         <v>0</v>
       </c>
-      <c r="G45" t="b">
-        <v>0</v>
+      <c r="G45" t="n">
+        <v>60</v>
       </c>
       <c r="H45" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2536,9 +2407,6 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2564,11 +2432,11 @@
       <c r="F46" t="b">
         <v>0</v>
       </c>
-      <c r="G46" t="b">
-        <v>0</v>
+      <c r="G46" t="n">
+        <v>60</v>
       </c>
       <c r="H46" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2577,9 +2445,6 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2605,22 +2470,19 @@
       <c r="F47" t="b">
         <v>0</v>
       </c>
-      <c r="G47" t="b">
-        <v>0</v>
+      <c r="G47" t="n">
+        <v>30</v>
       </c>
       <c r="H47" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I47" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
         <v>45</v>
       </c>
     </row>
@@ -2646,22 +2508,19 @@
       <c r="F48" t="b">
         <v>0</v>
       </c>
-      <c r="G48" t="b">
-        <v>0</v>
+      <c r="G48" t="n">
+        <v>30</v>
       </c>
       <c r="H48" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
         <v>45</v>
       </c>
     </row>
@@ -2687,11 +2546,11 @@
       <c r="F49" t="b">
         <v>0</v>
       </c>
-      <c r="G49" t="b">
-        <v>0</v>
+      <c r="G49" t="n">
+        <v>30</v>
       </c>
       <c r="H49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2700,9 +2559,6 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2728,13 +2584,10 @@
       <c r="F50" t="b">
         <v>0</v>
       </c>
-      <c r="G50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
+      <c r="K50" t="n">
         <v>90</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>COMPLEMENTAR</t>
         </is>
@@ -2765,25 +2618,22 @@
       <c r="F51" t="b">
         <v>1</v>
       </c>
-      <c r="G51" t="b">
-        <v>1</v>
+      <c r="G51" t="n">
+        <v>30</v>
       </c>
       <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
         <v>30</v>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
       <c r="J51" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>60</v>
-      </c>
-      <c r="M51" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -2814,11 +2664,11 @@
       <c r="F52" t="b">
         <v>1</v>
       </c>
-      <c r="G52" t="b">
-        <v>0</v>
+      <c r="G52" t="n">
+        <v>60</v>
       </c>
       <c r="H52" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -2827,12 +2677,9 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>60</v>
-      </c>
-      <c r="M52" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -2863,25 +2710,22 @@
       <c r="F53" t="b">
         <v>1</v>
       </c>
-      <c r="G53" t="b">
+      <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>30</v>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>30</v>
-      </c>
-      <c r="M53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -2909,11 +2753,11 @@
       <c r="F54" t="b">
         <v>0</v>
       </c>
-      <c r="G54" t="b">
-        <v>0</v>
+      <c r="G54" t="n">
+        <v>60</v>
       </c>
       <c r="H54" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2922,9 +2766,6 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2950,22 +2791,19 @@
       <c r="F55" t="b">
         <v>0</v>
       </c>
-      <c r="G55" t="b">
+      <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I55" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2994,25 +2832,22 @@
       <c r="F56" t="b">
         <v>1</v>
       </c>
-      <c r="G56" t="b">
-        <v>0</v>
+      <c r="G56" t="n">
+        <v>30</v>
       </c>
       <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>30</v>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>30</v>
-      </c>
-      <c r="M56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -3043,25 +2878,22 @@
       <c r="F57" t="b">
         <v>1</v>
       </c>
-      <c r="G57" t="b">
-        <v>1</v>
+      <c r="G57" t="n">
+        <v>15</v>
       </c>
       <c r="H57" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
         <v>45</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -3092,30 +2924,27 @@
       <c r="F58" t="b">
         <v>1</v>
       </c>
-      <c r="G58" t="b">
-        <v>1</v>
+      <c r="G58" t="n">
+        <v>45</v>
       </c>
       <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>45</v>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>45</v>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
       </c>
       <c r="M58" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
         <is>
           <t>Adaptável|Colaborativo|Orientado por Propósito</t>
         </is>
@@ -3146,25 +2975,22 @@
       <c r="F59" t="b">
         <v>1</v>
       </c>
-      <c r="G59" t="b">
-        <v>0</v>
+      <c r="G59" t="n">
+        <v>30</v>
       </c>
       <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>30</v>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>30</v>
-      </c>
-      <c r="M59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -3195,11 +3021,11 @@
       <c r="F60" t="b">
         <v>1</v>
       </c>
-      <c r="G60" t="b">
-        <v>0</v>
+      <c r="G60" t="n">
+        <v>60</v>
       </c>
       <c r="H60" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -3208,12 +3034,9 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>60</v>
-      </c>
-      <c r="M60" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -3244,11 +3067,11 @@
       <c r="F61" t="b">
         <v>1</v>
       </c>
-      <c r="G61" t="b">
-        <v>1</v>
+      <c r="G61" t="n">
+        <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -3257,17 +3080,14 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>60</v>
+        <v>60</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
       </c>
       <c r="M61" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
         <is>
           <t>Meticuloso|Inventivo|Adaptável</t>
         </is>
@@ -3295,22 +3115,19 @@
       <c r="F62" t="b">
         <v>0</v>
       </c>
-      <c r="G62" t="b">
-        <v>1</v>
+      <c r="G62" t="n">
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I62" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3336,22 +3153,19 @@
       <c r="F63" t="b">
         <v>0</v>
       </c>
-      <c r="G63" t="b">
-        <v>1</v>
+      <c r="G63" t="n">
+        <v>30</v>
       </c>
       <c r="H63" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J63" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3380,11 +3194,11 @@
       <c r="F64" t="b">
         <v>1</v>
       </c>
-      <c r="G64" t="b">
-        <v>0</v>
+      <c r="G64" t="n">
+        <v>60</v>
       </c>
       <c r="H64" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -3393,12 +3207,9 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>60</v>
-      </c>
-      <c r="M64" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -3429,25 +3240,22 @@
       <c r="F65" t="b">
         <v>1</v>
       </c>
-      <c r="G65" t="b">
+      <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>30</v>
       </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>30</v>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -3478,11 +3286,11 @@
       <c r="F66" t="b">
         <v>1</v>
       </c>
-      <c r="G66" t="b">
-        <v>0</v>
+      <c r="G66" t="n">
+        <v>60</v>
       </c>
       <c r="H66" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -3491,12 +3299,9 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>60</v>
-      </c>
-      <c r="M66" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -3527,25 +3332,22 @@
       <c r="F67" t="b">
         <v>1</v>
       </c>
-      <c r="G67" t="b">
+      <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>30</v>
       </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>30</v>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -3576,11 +3378,11 @@
       <c r="F68" t="b">
         <v>0</v>
       </c>
-      <c r="G68" t="b">
-        <v>0</v>
+      <c r="G68" t="n">
+        <v>60</v>
       </c>
       <c r="H68" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -3589,12 +3391,9 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>60</v>
-      </c>
-      <c r="M68" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -3625,25 +3424,22 @@
       <c r="F69" t="b">
         <v>0</v>
       </c>
-      <c r="G69" t="b">
+      <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
         <v>30</v>
       </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>30</v>
-      </c>
-      <c r="M69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -3671,22 +3467,19 @@
       <c r="F70" t="b">
         <v>0</v>
       </c>
-      <c r="G70" t="b">
-        <v>0</v>
+      <c r="G70" t="n">
+        <v>45</v>
       </c>
       <c r="H70" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I70" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3715,25 +3508,22 @@
       <c r="F71" t="b">
         <v>1</v>
       </c>
-      <c r="G71" t="b">
-        <v>1</v>
+      <c r="G71" t="n">
+        <v>30</v>
       </c>
       <c r="H71" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I71" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
         <v>45</v>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -3764,11 +3554,11 @@
       <c r="F72" t="b">
         <v>1</v>
       </c>
-      <c r="G72" t="b">
-        <v>0</v>
+      <c r="G72" t="n">
+        <v>60</v>
       </c>
       <c r="H72" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -3777,12 +3567,9 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>60</v>
-      </c>
-      <c r="M72" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -3810,11 +3597,11 @@
       <c r="F73" t="b">
         <v>0</v>
       </c>
-      <c r="G73" t="b">
-        <v>0</v>
+      <c r="G73" t="n">
+        <v>60</v>
       </c>
       <c r="H73" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -3823,9 +3610,6 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3851,25 +3635,22 @@
       <c r="F74" t="b">
         <v>1</v>
       </c>
-      <c r="G74" t="b">
-        <v>0</v>
+      <c r="G74" t="n">
+        <v>30</v>
       </c>
       <c r="H74" t="n">
         <v>30</v>
       </c>
       <c r="I74" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>60</v>
-      </c>
-      <c r="O74" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t>FAGEN39401 Empreendorismo e Inovação</t>
         </is>
@@ -3900,25 +3681,22 @@
       <c r="F75" t="b">
         <v>1</v>
       </c>
-      <c r="G75" t="b">
-        <v>1</v>
+      <c r="G75" t="n">
+        <v>15</v>
       </c>
       <c r="H75" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
         <v>45</v>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -3946,11 +3724,11 @@
       <c r="F76" t="b">
         <v>0</v>
       </c>
-      <c r="G76" t="b">
-        <v>0</v>
+      <c r="G76" t="n">
+        <v>30</v>
       </c>
       <c r="H76" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -3959,9 +3737,6 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3987,11 +3762,11 @@
       <c r="F77" t="b">
         <v>1</v>
       </c>
-      <c r="G77" t="b">
-        <v>0</v>
+      <c r="G77" t="n">
+        <v>60</v>
       </c>
       <c r="H77" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -4000,12 +3775,9 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>60</v>
-      </c>
-      <c r="O77" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t>FEELT!FIA Fundamentos da Inteligência Artificial</t>
         </is>
@@ -4033,11 +3805,11 @@
       <c r="F78" t="b">
         <v>1</v>
       </c>
-      <c r="G78" t="b">
-        <v>0</v>
+      <c r="G78" t="n">
+        <v>60</v>
       </c>
       <c r="H78" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -4046,12 +3818,9 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>60</v>
-      </c>
-      <c r="O78" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t>FEELT!FIA Fundamentos da Inteligência Artificial</t>
         </is>
@@ -4079,11 +3848,11 @@
       <c r="F79" t="b">
         <v>0</v>
       </c>
-      <c r="G79" t="b">
-        <v>0</v>
+      <c r="G79" t="n">
+        <v>60</v>
       </c>
       <c r="H79" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -4092,9 +3861,6 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4120,11 +3886,11 @@
       <c r="F80" t="b">
         <v>0</v>
       </c>
-      <c r="G80" t="b">
-        <v>0</v>
+      <c r="G80" t="n">
+        <v>60</v>
       </c>
       <c r="H80" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -4133,9 +3899,6 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4164,25 +3927,22 @@
       <c r="F81" t="b">
         <v>1</v>
       </c>
-      <c r="G81" t="b">
-        <v>1</v>
+      <c r="G81" t="n">
+        <v>30</v>
       </c>
       <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
         <v>30</v>
       </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>30</v>
-      </c>
-      <c r="M81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
@@ -4210,11 +3970,11 @@
       <c r="F82" t="b">
         <v>0</v>
       </c>
-      <c r="G82" t="b">
-        <v>0</v>
+      <c r="G82" t="n">
+        <v>60</v>
       </c>
       <c r="H82" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -4223,9 +3983,6 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4251,11 +4008,11 @@
       <c r="F83" t="b">
         <v>0</v>
       </c>
-      <c r="G83" t="b">
-        <v>0</v>
+      <c r="G83" t="n">
+        <v>60</v>
       </c>
       <c r="H83" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -4264,9 +4021,6 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4295,25 +4049,22 @@
       <c r="F84" t="b">
         <v>1</v>
       </c>
-      <c r="G84" t="b">
-        <v>0</v>
+      <c r="G84" t="n">
+        <v>30</v>
       </c>
       <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>30</v>
       </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>30</v>
-      </c>
-      <c r="M84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
@@ -4344,25 +4095,22 @@
       <c r="F85" t="b">
         <v>1</v>
       </c>
-      <c r="G85" t="b">
-        <v>1</v>
+      <c r="G85" t="n">
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
         <v>30</v>
       </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>30</v>
-      </c>
-      <c r="M85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -4390,22 +4138,19 @@
       <c r="F86" t="b">
         <v>0</v>
       </c>
-      <c r="G86" t="b">
-        <v>0</v>
+      <c r="G86" t="n">
+        <v>30</v>
       </c>
       <c r="H86" t="n">
         <v>30</v>
       </c>
       <c r="I86" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4431,22 +4176,19 @@
       <c r="F87" t="b">
         <v>0</v>
       </c>
-      <c r="G87" t="b">
-        <v>0</v>
+      <c r="G87" t="n">
+        <v>30</v>
       </c>
       <c r="H87" t="n">
         <v>30</v>
       </c>
       <c r="I87" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4472,11 +4214,11 @@
       <c r="F88" t="b">
         <v>1</v>
       </c>
-      <c r="G88" t="b">
-        <v>0</v>
+      <c r="G88" t="n">
+        <v>60</v>
       </c>
       <c r="H88" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4485,12 +4227,9 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>60</v>
-      </c>
-      <c r="O88" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>FEELT!TCOMP Teoria da Computação</t>
         </is>
@@ -4521,30 +4260,27 @@
       <c r="F89" t="b">
         <v>1</v>
       </c>
-      <c r="G89" t="b">
-        <v>1</v>
+      <c r="G89" t="n">
+        <v>45</v>
       </c>
       <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
         <v>45</v>
       </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>45</v>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>BASICO</t>
+        </is>
       </c>
       <c r="M89" t="inlineStr">
-        <is>
-          <t>BASICO</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
         <is>
           <t>Meticuloso|Adaptável|Orientado por Propósito</t>
         </is>
@@ -4575,8 +4311,8 @@
       <c r="F90" t="b">
         <v>0</v>
       </c>
-      <c r="G90" t="b">
-        <v>1</v>
+      <c r="G90" t="n">
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4585,15 +4321,12 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K90" t="n">
         <v>30</v>
       </c>
-      <c r="L90" t="n">
-        <v>30</v>
-      </c>
-      <c r="M90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
@@ -4624,25 +4357,22 @@
       <c r="F91" t="b">
         <v>1</v>
       </c>
-      <c r="G91" t="b">
-        <v>0</v>
+      <c r="G91" t="n">
+        <v>75</v>
       </c>
       <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>75</v>
       </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>75</v>
-      </c>
-      <c r="M91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -4673,25 +4403,22 @@
       <c r="F92" t="b">
         <v>1</v>
       </c>
-      <c r="G92" t="b">
-        <v>0</v>
+      <c r="G92" t="n">
+        <v>30</v>
       </c>
       <c r="H92" t="n">
         <v>30</v>
       </c>
       <c r="I92" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>60</v>
-      </c>
-      <c r="M92" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
@@ -4719,22 +4446,19 @@
       <c r="F93" t="b">
         <v>0</v>
       </c>
-      <c r="G93" t="b">
-        <v>0</v>
+      <c r="G93" t="n">
+        <v>30</v>
       </c>
       <c r="H93" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I93" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
         <v>45</v>
       </c>
     </row>
@@ -4760,11 +4484,11 @@
       <c r="F94" t="b">
         <v>0</v>
       </c>
-      <c r="G94" t="b">
-        <v>0</v>
+      <c r="G94" t="n">
+        <v>60</v>
       </c>
       <c r="H94" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -4773,9 +4497,6 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4801,11 +4522,11 @@
       <c r="F95" t="b">
         <v>0</v>
       </c>
-      <c r="G95" t="b">
-        <v>0</v>
+      <c r="G95" t="n">
+        <v>60</v>
       </c>
       <c r="H95" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -4814,9 +4535,6 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4842,11 +4560,11 @@
       <c r="F96" t="b">
         <v>0</v>
       </c>
-      <c r="G96" t="b">
-        <v>0</v>
+      <c r="G96" t="n">
+        <v>60</v>
       </c>
       <c r="H96" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4855,9 +4573,6 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4883,22 +4598,19 @@
       <c r="F97" t="b">
         <v>0</v>
       </c>
-      <c r="G97" t="b">
-        <v>0</v>
+      <c r="G97" t="n">
+        <v>45</v>
       </c>
       <c r="H97" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I97" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4924,22 +4636,19 @@
       <c r="F98" t="b">
         <v>0</v>
       </c>
-      <c r="G98" t="b">
-        <v>1</v>
+      <c r="G98" t="n">
+        <v>30</v>
       </c>
       <c r="H98" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I98" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
         <v>45</v>
       </c>
     </row>
@@ -4965,11 +4674,11 @@
       <c r="F99" t="b">
         <v>0</v>
       </c>
-      <c r="G99" t="b">
-        <v>0</v>
+      <c r="G99" t="n">
+        <v>60</v>
       </c>
       <c r="H99" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4978,9 +4687,6 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5006,22 +4712,19 @@
       <c r="F100" t="b">
         <v>0</v>
       </c>
-      <c r="G100" t="b">
-        <v>0</v>
+      <c r="G100" t="n">
+        <v>30</v>
       </c>
       <c r="H100" t="n">
         <v>30</v>
       </c>
       <c r="I100" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5047,11 +4750,11 @@
       <c r="F101" t="b">
         <v>0</v>
       </c>
-      <c r="G101" t="b">
-        <v>0</v>
+      <c r="G101" t="n">
+        <v>60</v>
       </c>
       <c r="H101" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -5060,9 +4763,6 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5088,11 +4788,11 @@
       <c r="F102" t="b">
         <v>0</v>
       </c>
-      <c r="G102" t="b">
-        <v>0</v>
+      <c r="G102" t="n">
+        <v>60</v>
       </c>
       <c r="H102" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -5101,9 +4801,6 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5129,22 +4826,19 @@
       <c r="F103" t="b">
         <v>0</v>
       </c>
-      <c r="G103" t="b">
-        <v>0</v>
+      <c r="G103" t="n">
+        <v>30</v>
       </c>
       <c r="H103" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
         <v>45</v>
       </c>
     </row>
@@ -5170,10 +4864,7 @@
       <c r="F104" t="b">
         <v>1</v>
       </c>
-      <c r="G104" t="b">
-        <v>1</v>
-      </c>
-      <c r="L104" t="n">
+      <c r="K104" t="n">
         <v>30</v>
       </c>
     </row>
@@ -5199,10 +4890,7 @@
       <c r="F105" t="b">
         <v>1</v>
       </c>
-      <c r="G105" t="b">
-        <v>1</v>
-      </c>
-      <c r="L105" t="n">
+      <c r="K105" t="n">
         <v>45</v>
       </c>
     </row>
@@ -5228,10 +4916,7 @@
       <c r="F106" t="b">
         <v>1</v>
       </c>
-      <c r="G106" t="b">
-        <v>1</v>
-      </c>
-      <c r="L106" t="n">
+      <c r="K106" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5257,10 +4942,7 @@
       <c r="F107" t="b">
         <v>1</v>
       </c>
-      <c r="G107" t="b">
-        <v>1</v>
-      </c>
-      <c r="L107" t="n">
+      <c r="K107" t="n">
         <v>75</v>
       </c>
     </row>
@@ -5286,22 +4968,19 @@
       <c r="F108" t="b">
         <v>0</v>
       </c>
-      <c r="G108" t="b">
-        <v>0</v>
+      <c r="G108" t="n">
+        <v>30</v>
       </c>
       <c r="H108" t="n">
         <v>30</v>
       </c>
       <c r="I108" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5327,22 +5006,19 @@
       <c r="F109" t="b">
         <v>0</v>
       </c>
-      <c r="G109" t="b">
-        <v>0</v>
+      <c r="G109" t="n">
+        <v>30</v>
       </c>
       <c r="H109" t="n">
         <v>30</v>
       </c>
       <c r="I109" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5368,11 +5044,11 @@
       <c r="F110" t="b">
         <v>0</v>
       </c>
-      <c r="G110" t="b">
-        <v>0</v>
+      <c r="G110" t="n">
+        <v>60</v>
       </c>
       <c r="H110" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -5381,9 +5057,6 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5409,11 +5082,11 @@
       <c r="F111" t="b">
         <v>0</v>
       </c>
-      <c r="G111" t="b">
-        <v>0</v>
+      <c r="G111" t="n">
+        <v>60</v>
       </c>
       <c r="H111" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -5422,9 +5095,6 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5453,25 +5123,22 @@
       <c r="F112" t="b">
         <v>1</v>
       </c>
-      <c r="G112" t="b">
-        <v>0</v>
+      <c r="G112" t="n">
+        <v>45</v>
       </c>
       <c r="H112" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I112" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" t="n">
-        <v>60</v>
-      </c>
-      <c r="M112" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -5502,30 +5169,27 @@
       <c r="F113" t="b">
         <v>1</v>
       </c>
-      <c r="G113" t="b">
-        <v>1</v>
+      <c r="G113" t="n">
+        <v>30</v>
       </c>
       <c r="H113" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I113" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
         <v>45</v>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
         <is>
           <t>Inventivo|Meticuloso|Autodirigido</t>
         </is>
@@ -5553,25 +5217,22 @@
       <c r="F114" t="b">
         <v>1</v>
       </c>
-      <c r="G114" t="b">
-        <v>0</v>
+      <c r="G114" t="n">
+        <v>30</v>
       </c>
       <c r="H114" t="n">
         <v>30</v>
       </c>
       <c r="I114" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="n">
-        <v>60</v>
-      </c>
-      <c r="O114" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t>FEELT!PF Programação Funcional</t>
         </is>
@@ -5599,22 +5260,19 @@
       <c r="F115" t="b">
         <v>0</v>
       </c>
-      <c r="G115" t="b">
-        <v>0</v>
+      <c r="G115" t="n">
+        <v>30</v>
       </c>
       <c r="H115" t="n">
         <v>30</v>
       </c>
       <c r="I115" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5640,22 +5298,19 @@
       <c r="F116" t="b">
         <v>0</v>
       </c>
-      <c r="G116" t="b">
-        <v>0</v>
+      <c r="G116" t="n">
+        <v>30</v>
       </c>
       <c r="H116" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I116" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
         <v>45</v>
       </c>
     </row>
@@ -5684,25 +5339,22 @@
       <c r="F117" t="b">
         <v>1</v>
       </c>
-      <c r="G117" t="b">
-        <v>1</v>
+      <c r="G117" t="n">
+        <v>30</v>
       </c>
       <c r="H117" t="n">
         <v>30</v>
       </c>
       <c r="I117" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>60</v>
-      </c>
-      <c r="M117" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -5730,22 +5382,19 @@
       <c r="F118" t="b">
         <v>0</v>
       </c>
-      <c r="G118" t="b">
-        <v>0</v>
+      <c r="G118" t="n">
+        <v>30</v>
       </c>
       <c r="H118" t="n">
         <v>30</v>
       </c>
       <c r="I118" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5771,22 +5420,19 @@
       <c r="F119" t="b">
         <v>0</v>
       </c>
-      <c r="G119" t="b">
-        <v>0</v>
+      <c r="G119" t="n">
+        <v>30</v>
       </c>
       <c r="H119" t="n">
         <v>30</v>
       </c>
       <c r="I119" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5812,11 +5458,11 @@
       <c r="F120" t="b">
         <v>0</v>
       </c>
-      <c r="G120" t="b">
-        <v>0</v>
+      <c r="G120" t="n">
+        <v>60</v>
       </c>
       <c r="H120" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -5825,9 +5471,6 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5856,30 +5499,27 @@
       <c r="F121" t="b">
         <v>1</v>
       </c>
-      <c r="G121" t="b">
-        <v>1</v>
+      <c r="G121" t="n">
+        <v>30</v>
       </c>
       <c r="H121" t="n">
         <v>30</v>
       </c>
       <c r="I121" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>60</v>
+        <v>60</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
       </c>
       <c r="M121" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
         <is>
           <t>Meticuloso|Inventivo|Adaptável</t>
         </is>
@@ -5910,30 +5550,27 @@
       <c r="F122" t="b">
         <v>1</v>
       </c>
-      <c r="G122" t="b">
-        <v>1</v>
+      <c r="G122" t="n">
+        <v>30</v>
       </c>
       <c r="H122" t="n">
         <v>30</v>
       </c>
       <c r="I122" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>60</v>
+        <v>60</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
       </c>
       <c r="M122" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
         <is>
           <t>Autodirigido|Meticuloso|Inventivo</t>
         </is>
@@ -5964,25 +5601,22 @@
       <c r="F123" t="b">
         <v>0</v>
       </c>
-      <c r="G123" t="b">
-        <v>1</v>
+      <c r="G123" t="n">
+        <v>30</v>
       </c>
       <c r="H123" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I123" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="n">
         <v>45</v>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6010,22 +5644,19 @@
       <c r="F124" t="b">
         <v>0</v>
       </c>
-      <c r="G124" t="b">
-        <v>0</v>
+      <c r="G124" t="n">
+        <v>45</v>
       </c>
       <c r="H124" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I124" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6054,25 +5685,22 @@
       <c r="F125" t="b">
         <v>0</v>
       </c>
-      <c r="G125" t="b">
-        <v>1</v>
+      <c r="G125" t="n">
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
         <v>45</v>
       </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" t="n">
-        <v>45</v>
-      </c>
-      <c r="M125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6100,22 +5728,19 @@
       <c r="F126" t="b">
         <v>0</v>
       </c>
-      <c r="G126" t="b">
-        <v>1</v>
+      <c r="G126" t="n">
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I126" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6144,25 +5769,22 @@
       <c r="F127" t="b">
         <v>1</v>
       </c>
-      <c r="G127" t="b">
-        <v>0</v>
+      <c r="G127" t="n">
+        <v>45</v>
       </c>
       <c r="H127" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I127" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
-        <v>60</v>
-      </c>
-      <c r="M127" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6193,25 +5815,22 @@
       <c r="F128" t="b">
         <v>1</v>
       </c>
-      <c r="G128" t="b">
-        <v>0</v>
+      <c r="G128" t="n">
+        <v>45</v>
       </c>
       <c r="H128" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I128" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>60</v>
-      </c>
-      <c r="M128" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6239,22 +5858,19 @@
       <c r="F129" t="b">
         <v>0</v>
       </c>
-      <c r="G129" t="b">
-        <v>0</v>
+      <c r="G129" t="n">
+        <v>45</v>
       </c>
       <c r="H129" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I129" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6280,25 +5896,22 @@
       <c r="F130" t="b">
         <v>1</v>
       </c>
-      <c r="G130" t="b">
-        <v>0</v>
+      <c r="G130" t="n">
+        <v>60</v>
       </c>
       <c r="H130" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I130" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="n">
         <v>75</v>
       </c>
-      <c r="O130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t>FEELT31724 Redes de Comunicações I</t>
         </is>
@@ -6326,25 +5939,22 @@
       <c r="F131" t="b">
         <v>1</v>
       </c>
-      <c r="G131" t="b">
-        <v>0</v>
+      <c r="G131" t="n">
+        <v>30</v>
       </c>
       <c r="H131" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I131" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="n">
         <v>90</v>
       </c>
-      <c r="O131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t>FEELT31831 Redes de Comunicações II</t>
         </is>
@@ -6372,22 +5982,19 @@
       <c r="F132" t="b">
         <v>0</v>
       </c>
-      <c r="G132" t="b">
-        <v>0</v>
+      <c r="G132" t="n">
+        <v>30</v>
       </c>
       <c r="H132" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I132" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6413,22 +6020,19 @@
       <c r="F133" t="b">
         <v>0</v>
       </c>
-      <c r="G133" t="b">
-        <v>1</v>
+      <c r="G133" t="n">
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I133" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6454,22 +6058,19 @@
       <c r="F134" t="b">
         <v>0</v>
       </c>
-      <c r="G134" t="b">
-        <v>1</v>
+      <c r="G134" t="n">
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I134" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6495,22 +6096,19 @@
       <c r="F135" t="b">
         <v>0</v>
       </c>
-      <c r="G135" t="b">
-        <v>0</v>
+      <c r="G135" t="n">
+        <v>45</v>
       </c>
       <c r="H135" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I135" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6539,25 +6137,22 @@
       <c r="F136" t="b">
         <v>1</v>
       </c>
-      <c r="G136" t="b">
-        <v>1</v>
+      <c r="G136" t="n">
+        <v>15</v>
       </c>
       <c r="H136" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J136" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
         <v>45</v>
       </c>
-      <c r="M136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6585,22 +6180,19 @@
       <c r="F137" t="b">
         <v>0</v>
       </c>
-      <c r="G137" t="b">
-        <v>0</v>
+      <c r="G137" t="n">
+        <v>30</v>
       </c>
       <c r="H137" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I137" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6629,25 +6221,22 @@
       <c r="F138" t="b">
         <v>1</v>
       </c>
-      <c r="G138" t="b">
-        <v>1</v>
+      <c r="G138" t="n">
+        <v>15</v>
       </c>
       <c r="H138" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I138" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
         <v>45</v>
       </c>
-      <c r="M138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6675,25 +6264,22 @@
       <c r="F139" t="b">
         <v>1</v>
       </c>
-      <c r="G139" t="b">
-        <v>0</v>
+      <c r="G139" t="n">
+        <v>60</v>
       </c>
       <c r="H139" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I139" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" t="n">
         <v>90</v>
       </c>
-      <c r="O139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t>FEELT!BD Banco de Dados</t>
         </is>
@@ -6724,25 +6310,22 @@
       <c r="F140" t="b">
         <v>1</v>
       </c>
-      <c r="G140" t="b">
-        <v>0</v>
+      <c r="G140" t="n">
+        <v>30</v>
       </c>
       <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
         <v>30</v>
       </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="n">
-        <v>30</v>
-      </c>
-      <c r="M140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6773,25 +6356,22 @@
       <c r="F141" t="b">
         <v>1</v>
       </c>
-      <c r="G141" t="b">
+      <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
         <v>30</v>
       </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" t="n">
-        <v>30</v>
-      </c>
-      <c r="M141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6822,25 +6402,22 @@
       <c r="F142" t="b">
         <v>1</v>
       </c>
-      <c r="G142" t="b">
-        <v>1</v>
+      <c r="G142" t="n">
+        <v>45</v>
       </c>
       <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
         <v>45</v>
       </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" t="n">
-        <v>45</v>
-      </c>
-      <c r="M142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -6868,11 +6445,11 @@
       <c r="F143" t="b">
         <v>1</v>
       </c>
-      <c r="G143" t="b">
-        <v>0</v>
+      <c r="G143" t="n">
+        <v>60</v>
       </c>
       <c r="H143" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -6881,12 +6458,9 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" t="n">
-        <v>60</v>
-      </c>
-      <c r="O143" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t>FEELT!SD Sistemas Distribuídos</t>
         </is>
@@ -6914,11 +6488,11 @@
       <c r="F144" t="b">
         <v>1</v>
       </c>
-      <c r="G144" t="b">
-        <v>0</v>
+      <c r="G144" t="n">
+        <v>60</v>
       </c>
       <c r="H144" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -6927,12 +6501,9 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" t="n">
-        <v>60</v>
-      </c>
-      <c r="O144" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t>FEELT!SD Sistemas Distribuídos</t>
         </is>
@@ -6963,25 +6534,22 @@
       <c r="F145" t="b">
         <v>1</v>
       </c>
-      <c r="G145" t="b">
-        <v>1</v>
+      <c r="G145" t="n">
+        <v>30</v>
       </c>
       <c r="H145" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I145" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" t="n">
         <v>45</v>
       </c>
-      <c r="M145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -7012,25 +6580,22 @@
       <c r="F146" t="b">
         <v>1</v>
       </c>
-      <c r="G146" t="b">
-        <v>0</v>
+      <c r="G146" t="n">
+        <v>45</v>
       </c>
       <c r="H146" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I146" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" t="n">
         <v>75</v>
       </c>
-      <c r="M146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -7058,22 +6623,19 @@
       <c r="F147" t="b">
         <v>0</v>
       </c>
-      <c r="G147" t="b">
-        <v>0</v>
+      <c r="G147" t="n">
+        <v>30</v>
       </c>
       <c r="H147" t="n">
         <v>30</v>
       </c>
       <c r="I147" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" t="n">
         <v>60</v>
       </c>
     </row>
@@ -7102,25 +6664,22 @@
       <c r="F148" t="b">
         <v>1</v>
       </c>
-      <c r="G148" t="b">
-        <v>1</v>
+      <c r="G148" t="n">
+        <v>45</v>
       </c>
       <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
         <v>45</v>
       </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" t="n">
-        <v>45</v>
-      </c>
-      <c r="M148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
@@ -7148,25 +6707,22 @@
       <c r="F149" t="b">
         <v>1</v>
       </c>
-      <c r="G149" t="b">
-        <v>0</v>
+      <c r="G149" t="n">
+        <v>60</v>
       </c>
       <c r="H149" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I149" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" t="n">
         <v>90</v>
       </c>
-      <c r="O149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t>FEELT!SO Sistemas Operacionais</t>
         </is>
@@ -7194,22 +6750,19 @@
       <c r="F150" t="b">
         <v>0</v>
       </c>
-      <c r="G150" t="b">
-        <v>0</v>
+      <c r="G150" t="n">
+        <v>30</v>
       </c>
       <c r="H150" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I150" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7238,30 +6791,27 @@
       <c r="F151" t="b">
         <v>1</v>
       </c>
-      <c r="G151" t="b">
-        <v>1</v>
+      <c r="G151" t="n">
+        <v>45</v>
       </c>
       <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
         <v>45</v>
       </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" t="n">
-        <v>45</v>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
       </c>
       <c r="M151" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
         <is>
           <t>Meticuloso|Adaptável|Inventivo</t>
         </is>
@@ -7289,10 +6839,7 @@
       <c r="F152" t="b">
         <v>0</v>
       </c>
-      <c r="G152" t="b">
-        <v>1</v>
-      </c>
-      <c r="L152" t="n">
+      <c r="K152" t="n">
         <v>30</v>
       </c>
     </row>
@@ -7318,10 +6865,7 @@
       <c r="F153" t="b">
         <v>0</v>
       </c>
-      <c r="G153" t="b">
-        <v>1</v>
-      </c>
-      <c r="L153" t="n">
+      <c r="K153" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7347,10 +6891,7 @@
       <c r="F154" t="b">
         <v>0</v>
       </c>
-      <c r="G154" t="b">
-        <v>1</v>
-      </c>
-      <c r="L154" t="n">
+      <c r="K154" t="n">
         <v>60</v>
       </c>
     </row>
@@ -7376,10 +6917,7 @@
       <c r="F155" t="b">
         <v>0</v>
       </c>
-      <c r="G155" t="b">
-        <v>1</v>
-      </c>
-      <c r="L155" t="n">
+      <c r="K155" t="n">
         <v>75</v>
       </c>
     </row>
@@ -7405,22 +6943,19 @@
       <c r="F156" t="b">
         <v>0</v>
       </c>
-      <c r="G156" t="b">
-        <v>0</v>
+      <c r="G156" t="n">
+        <v>30</v>
       </c>
       <c r="H156" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I156" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7446,22 +6981,19 @@
       <c r="F157" t="b">
         <v>0</v>
       </c>
-      <c r="G157" t="b">
-        <v>0</v>
+      <c r="G157" t="n">
+        <v>30</v>
       </c>
       <c r="H157" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I157" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7487,22 +7019,19 @@
       <c r="F158" t="b">
         <v>0</v>
       </c>
-      <c r="G158" t="b">
-        <v>0</v>
+      <c r="G158" t="n">
+        <v>30</v>
       </c>
       <c r="H158" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I158" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7528,22 +7057,19 @@
       <c r="F159" t="b">
         <v>0</v>
       </c>
-      <c r="G159" t="b">
-        <v>0</v>
+      <c r="G159" t="n">
+        <v>30</v>
       </c>
       <c r="H159" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I159" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7569,22 +7095,19 @@
       <c r="F160" t="b">
         <v>0</v>
       </c>
-      <c r="G160" t="b">
-        <v>0</v>
+      <c r="G160" t="n">
+        <v>30</v>
       </c>
       <c r="H160" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I160" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7595,12 +7118,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Planilha3">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="18.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8469,12 +7996,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Planilha4">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="18.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8620,12 +8152,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Planilha5">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B65"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="18.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="37.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -9414,12 +8950,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Planilha6">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="18.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="25.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -9632,12 +9172,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Planilha7">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B171"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="18.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -11698,12 +11242,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Planilha8">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
